--- a/artfynd/A 50352-2025 artfynd.xlsx
+++ b/artfynd/A 50352-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532973</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128532970</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128532972</v>
       </c>
       <c r="B4" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128532974</v>
       </c>
       <c r="B5" t="n">
-        <v>79619</v>
+        <v>79624</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128532971</v>
       </c>
       <c r="B6" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50352-2025 artfynd.xlsx
+++ b/artfynd/A 50352-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128532973</v>
+        <v>128532970</v>
       </c>
       <c r="B2" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766430</v>
+        <v>766371</v>
       </c>
       <c r="R2" t="n">
-        <v>7289746</v>
+        <v>7289566</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128532970</v>
+        <v>128532973</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766371</v>
+        <v>766430</v>
       </c>
       <c r="R3" t="n">
-        <v>7289566</v>
+        <v>7289746</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128532972</v>
+        <v>128532974</v>
       </c>
       <c r="B4" t="n">
-        <v>80168</v>
+        <v>79624</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766097</v>
+        <v>766430</v>
       </c>
       <c r="R4" t="n">
-        <v>7289559</v>
+        <v>7289746</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128532974</v>
+        <v>128532972</v>
       </c>
       <c r="B5" t="n">
-        <v>79624</v>
+        <v>80168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766430</v>
+        <v>766097</v>
       </c>
       <c r="R5" t="n">
-        <v>7289746</v>
+        <v>7289559</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1208,7 +1208,7 @@
         <v>129001301</v>
       </c>
       <c r="B7" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50352-2025 artfynd.xlsx
+++ b/artfynd/A 50352-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532970</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128532973</v>
       </c>
       <c r="B3" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128532974</v>
+        <v>128532972</v>
       </c>
       <c r="B4" t="n">
-        <v>79624</v>
+        <v>80169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766430</v>
+        <v>766097</v>
       </c>
       <c r="R4" t="n">
-        <v>7289746</v>
+        <v>7289559</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128532972</v>
+        <v>128532974</v>
       </c>
       <c r="B5" t="n">
-        <v>80168</v>
+        <v>79625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766097</v>
+        <v>766430</v>
       </c>
       <c r="R5" t="n">
-        <v>7289559</v>
+        <v>7289746</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1102,7 +1102,7 @@
         <v>128532971</v>
       </c>
       <c r="B6" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129001301</v>
       </c>
       <c r="B7" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50352-2025 artfynd.xlsx
+++ b/artfynd/A 50352-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>129001301</v>
       </c>
       <c r="B7" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50352-2025 artfynd.xlsx
+++ b/artfynd/A 50352-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>129001301</v>
       </c>
       <c r="B7" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50352-2025 artfynd.xlsx
+++ b/artfynd/A 50352-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>129001301</v>
       </c>
       <c r="B7" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50352-2025 artfynd.xlsx
+++ b/artfynd/A 50352-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>129001301</v>
       </c>
       <c r="B7" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50352-2025 artfynd.xlsx
+++ b/artfynd/A 50352-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>129001301</v>
       </c>
       <c r="B7" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50352-2025 artfynd.xlsx
+++ b/artfynd/A 50352-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>129001301</v>
       </c>
       <c r="B7" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50352-2025 artfynd.xlsx
+++ b/artfynd/A 50352-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128532970</v>
+        <v>129001301</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>93209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766371</v>
+        <v>766148</v>
       </c>
       <c r="R2" t="n">
-        <v>7289566</v>
+        <v>7289207</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128532973</v>
+        <v>128532970</v>
       </c>
       <c r="B3" t="n">
-        <v>78792</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766430</v>
+        <v>766371</v>
       </c>
       <c r="R3" t="n">
-        <v>7289746</v>
+        <v>7289566</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128532972</v>
+        <v>128532973</v>
       </c>
       <c r="B4" t="n">
-        <v>80169</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766097</v>
+        <v>766430</v>
       </c>
       <c r="R4" t="n">
-        <v>7289559</v>
+        <v>7289746</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128532974</v>
+        <v>128532971</v>
       </c>
       <c r="B5" t="n">
-        <v>79625</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766430</v>
+        <v>766121</v>
       </c>
       <c r="R5" t="n">
-        <v>7289746</v>
+        <v>7289557</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128532971</v>
+        <v>128532972</v>
       </c>
       <c r="B6" t="n">
-        <v>80140</v>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>766121</v>
+        <v>766097</v>
       </c>
       <c r="R6" t="n">
-        <v>7289557</v>
+        <v>7289559</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129001301</v>
+        <v>128532974</v>
       </c>
       <c r="B7" t="n">
-        <v>92847</v>
+        <v>79917</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>766148</v>
+        <v>766430</v>
       </c>
       <c r="R7" t="n">
-        <v>7289207</v>
+        <v>7289746</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 50352-2025 artfynd.xlsx
+++ b/artfynd/A 50352-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001301</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128532970</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128532973</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128532971</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128532972</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,8 +1338,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128532974</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>